--- a/Fase_2/Evidencias Proyecto/Evidencias de documentación/Listo/PMOInformatica_Product_Backlog_SIGFQ.xlsx
+++ b/Fase_2/Evidencias Proyecto/Evidencias de documentación/Listo/PMOInformatica_Product_Backlog_SIGFQ.xlsx
@@ -17,60 +17,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="183">
+  <si>
+    <t>Pila de Producto (Product Backlog): Instructivo</t>
+  </si>
   <si>
     <t>Desarrollo ágil: Pila de Producto (Product Backlog)</t>
   </si>
   <si>
-    <t>Pila de Producto (Product Backlog): Instructivo</t>
+    <t>Elaborado por: pmoinformatica.com</t>
   </si>
   <si>
     <t>Product Backlog; planificación en Sprint Planning del 07/09/2026</t>
   </si>
   <si>
-    <t>Elaborado por: pmoinformatica.com</t>
+    <t>Columna</t>
+  </si>
+  <si>
+    <t>Instrucciones</t>
   </si>
   <si>
     <t>Identificador (ID) de la Historia</t>
   </si>
   <si>
-    <t>Columna</t>
+    <t>Código que identifica a la historia de forma unívoca, una vez asignado, no debe ser re-usado en otra historia, ni siquiera si la historia es descartada. El código identifica la historia en otros documentos, como por ejemplo la plantilla de historias de usuario.</t>
   </si>
   <si>
     <t>Enunciado de la Historia</t>
-  </si>
-  <si>
-    <t>Alias</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Dimensión / Esfuerzo</t>
-  </si>
-  <si>
-    <t>Iteración (Sprint)</t>
-  </si>
-  <si>
-    <t>Prioridad</t>
-  </si>
-  <si>
-    <t>Instrucciones</t>
-  </si>
-  <si>
-    <t>Comentarios</t>
-  </si>
-  <si>
-    <t>E1-H1</t>
-  </si>
-  <si>
-    <t>Como Usuario interno, necesito iniciar sesión en la plataforma, con la finalidad de acceder de forma segura a las funciones autorizadas.</t>
-  </si>
-  <si>
-    <t>Código que identifica a la historia de forma unívoca, una vez asignado, no debe ser re-usado en otra historia, ni siquiera si la historia es descartada. El código identifica la historia en otros documentos, como por ejemplo la plantilla de historias de usuario.</t>
-  </si>
-  <si>
-    <t>Iniciar sesión en la plataforma</t>
   </si>
   <si>
     <t xml:space="preserve">Nombre de la historia, el cual debe ser el mismo que se utiliza en otros documentos. Se puede utilizar el formato siguiente:
@@ -78,13 +51,25 @@
 </t>
   </si>
   <si>
-    <t>Hecho</t>
+    <t>Alias</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Dimensión / Esfuerzo</t>
   </si>
   <si>
     <t>Título de la historia alternativo a la descripción, que servirá para identificar más fácilmente la historia sin tener que repetir todo su enunciado. Se puede utilizar por ejemplo el nombre de la funcionalidad o requerimiento que se pretende desarrollar.</t>
   </si>
   <si>
-    <t>Sprint 1</t>
+    <t>Iteración (Sprint)</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
+    <t>Comentarios</t>
   </si>
   <si>
     <t xml:space="preserve">Identifica los posibles estados de la historia durante su ciclo de vida:
@@ -96,18 +81,36 @@
 </t>
   </si>
   <si>
+    <t>Medida del esfuerzo (tamaño) que implica desarrollar la historia, existen distintos métodos para medirlo, un ejemplo es los “puntos de historia” una medida de complejidad no necesariamente relacionado con jornadas o días. Otra forma de medirlo es con días o jornadas ideales.</t>
+  </si>
+  <si>
+    <t>E1-H1</t>
+  </si>
+  <si>
+    <t>Iteración o Sprint al que se asigna la historia. Esta asignación puede cambiar en cada iteración donde se haga la revisión de la pila de producto (ProductBacklogReview), según las prioridades indicadas por el dueño de producto. Por medio de este campo se puede crear un “Plan de Salidas a Productivo” (Release Plan).</t>
+  </si>
+  <si>
+    <t>Como Usuario interno, necesito iniciar sesión en la plataforma, con la finalidad de acceder de forma segura a las funciones autorizadas.</t>
+  </si>
+  <si>
+    <t>Iniciar sesión en la plataforma</t>
+  </si>
+  <si>
+    <t>Siguiendo el marco de trabajo ágil y Scrum, se le deben asignar prioridades a las historias, según las instrucciones del dueño de producto (ProductOwner). De esta forma pueden ordenarse. Las historias de mayor prioridad deben ser las que agregan más valor al negocio, y deben ser originadas en sus necesidades.</t>
+  </si>
+  <si>
+    <t>Comentarios o detalles relacionadas que expliquen la historia. Para definiciones de mayor longitud deben usarse documentos externos, por ejemplo la plantilla de historias de usuario.</t>
+  </si>
+  <si>
+    <t>Hecho</t>
+  </si>
+  <si>
+    <t>Sprint 1</t>
+  </si>
+  <si>
     <t>Alta (Must)</t>
   </si>
   <si>
-    <t>Medida del esfuerzo (tamaño) que implica desarrollar la historia, existen distintos métodos para medirlo, un ejemplo es los “puntos de historia” una medida de complejidad no necesariamente relacionado con jornadas o días. Otra forma de medirlo es con días o jornadas ideales.</t>
-  </si>
-  <si>
-    <t>Iteración o Sprint al que se asigna la historia. Esta asignación puede cambiar en cada iteración donde se haga la revisión de la pila de producto (ProductBacklogReview), según las prioridades indicadas por el dueño de producto. Por medio de este campo se puede crear un “Plan de Salidas a Productivo” (Release Plan).</t>
-  </si>
-  <si>
-    <t>Siguiendo el marco de trabajo ágil y Scrum, se le deben asignar prioridades a las historias, según las instrucciones del dueño de producto (ProductOwner). De esta forma pueden ordenarse. Las historias de mayor prioridad deben ser las que agregan más valor al negocio, y deben ser originadas en sus necesidades.</t>
-  </si>
-  <si>
     <t>Sin dependencia funcional directa.</t>
   </si>
   <si>
@@ -120,9 +123,6 @@
     <t>Crear, actualizar y desactivar usuarios internos</t>
   </si>
   <si>
-    <t>Comentarios o detalles relacionadas que expliquen la historia. Para definiciones de mayor longitud deben usarse documentos externos, por ejemplo la plantilla de historias de usuario.</t>
-  </si>
-  <si>
     <t>Depende de E1-H1.</t>
   </si>
   <si>
@@ -409,9 +409,6 @@
   </si>
   <si>
     <t>Comprar sin crear una cuenta</t>
-  </si>
-  <si>
-    <t>En Proceso</t>
   </si>
   <si>
     <t>E6-H4</t>
@@ -608,15 +605,20 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="16.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <sz val="9.0"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="16.0"/>
-      <color rgb="FF1F497D"/>
+      <sz val="11.0"/>
+      <color theme="0"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -628,11 +630,6 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF1F1F1F"/>
@@ -670,14 +667,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF1F4E78"/>
+        <fgColor rgb="FF1F497D"/>
+        <bgColor rgb="FF1F497D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F497D"/>
-        <bgColor rgb="FF1F497D"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
@@ -703,6 +700,20 @@
     <border/>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFA6A6A6"/>
       </left>
       <right style="thin">
@@ -713,20 +724,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFA6A6A6"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
@@ -754,23 +751,23 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -1052,7 +1049,7 @@
     <row r="1" ht="36.75" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1074,8 +1071,8 @@
     </row>
     <row r="2" ht="39.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1097,14 +1094,14 @@
     </row>
     <row r="3">
       <c r="A3" s="1"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1125,29 +1122,29 @@
     </row>
     <row r="4" ht="33.75" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>13</v>
+      <c r="F4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1168,96 +1165,96 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10" t="s">
-        <v>14</v>
+      <c r="A5" s="10"/>
+      <c r="B5" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F5" s="13">
         <v>3.0</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>21</v>
+      <c r="G5" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
     </row>
     <row r="6">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10" t="s">
-        <v>28</v>
+      <c r="A6" s="10"/>
+      <c r="B6" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F6" s="13">
         <v>5.0</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>21</v>
+      <c r="G6" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
     </row>
     <row r="7">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="12" t="s">
@@ -1266,42 +1263,42 @@
       <c r="D7" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>19</v>
+      <c r="E7" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F7" s="13">
         <v>5.0</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>21</v>
+      <c r="G7" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
     </row>
     <row r="8">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -1310,42 +1307,42 @@
       <c r="D8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>19</v>
+      <c r="E8" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F8" s="13">
         <v>3.0</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>21</v>
+      <c r="G8" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
     </row>
     <row r="9">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11" t="s">
         <v>41</v>
       </c>
       <c r="C9" s="12" t="s">
@@ -1354,42 +1351,42 @@
       <c r="D9" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>19</v>
+      <c r="E9" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F9" s="13">
         <v>5.0</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>21</v>
+      <c r="G9" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
     </row>
     <row r="10">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -1398,42 +1395,42 @@
       <c r="D10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>19</v>
+      <c r="E10" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F10" s="13">
         <v>8.0</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
     </row>
     <row r="11">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10" t="s">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="12" t="s">
@@ -1442,42 +1439,42 @@
       <c r="D11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>19</v>
+      <c r="E11" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F11" s="13">
         <v>5.0</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
     </row>
     <row r="12">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -1486,42 +1483,42 @@
       <c r="D12" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>19</v>
+      <c r="E12" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F12" s="13">
         <v>5.0</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
     </row>
     <row r="13">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -1530,42 +1527,42 @@
       <c r="D13" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>19</v>
+      <c r="E13" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F13" s="13">
         <v>3.0</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
     </row>
     <row r="14">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="12" t="s">
@@ -1574,42 +1571,42 @@
       <c r="D14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>19</v>
+      <c r="E14" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F14" s="13">
         <v>5.0</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
     </row>
     <row r="15">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="12" t="s">
@@ -1618,42 +1615,42 @@
       <c r="D15" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>19</v>
+      <c r="E15" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F15" s="13">
         <v>8.0</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
     </row>
     <row r="16">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10" t="s">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11" t="s">
         <v>67</v>
       </c>
       <c r="C16" s="12" t="s">
@@ -1662,42 +1659,42 @@
       <c r="D16" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>19</v>
+      <c r="E16" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F16" s="13">
         <v>3.0</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
     </row>
     <row r="17">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="12" t="s">
@@ -1706,42 +1703,42 @@
       <c r="D17" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>19</v>
+      <c r="E17" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F17" s="13">
         <v>8.0</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="9"/>
-      <c r="Z17" s="9"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
     </row>
     <row r="18">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10" t="s">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11" t="s">
         <v>74</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -1750,41 +1747,41 @@
       <c r="D18" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>19</v>
+      <c r="E18" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F18" s="13">
         <v>8.0</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
     </row>
     <row r="19">
-      <c r="A19" s="9"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="15" t="s">
         <v>78</v>
       </c>
@@ -1794,41 +1791,41 @@
       <c r="D19" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>19</v>
+      <c r="E19" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F19" s="17">
         <v>5.0</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I19" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
     </row>
     <row r="20">
-      <c r="A20" s="9"/>
+      <c r="A20" s="10"/>
       <c r="B20" s="15" t="s">
         <v>82</v>
       </c>
@@ -1838,41 +1835,41 @@
       <c r="D20" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>19</v>
+      <c r="E20" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F20" s="17">
         <v>5.0</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I20" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
     </row>
     <row r="21">
-      <c r="A21" s="9"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="15" t="s">
         <v>86</v>
       </c>
@@ -1882,41 +1879,41 @@
       <c r="D21" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>19</v>
+      <c r="E21" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F21" s="17">
         <v>8.0</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="9"/>
-      <c r="Z21" s="9"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
     </row>
     <row r="22">
-      <c r="A22" s="9"/>
+      <c r="A22" s="10"/>
       <c r="B22" s="15" t="s">
         <v>90</v>
       </c>
@@ -1926,41 +1923,41 @@
       <c r="D22" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>19</v>
+      <c r="E22" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="F22" s="17">
         <v>5.0</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="10"/>
     </row>
     <row r="23">
-      <c r="A23" s="9"/>
+      <c r="A23" s="10"/>
       <c r="B23" s="15" t="s">
         <v>94</v>
       </c>
@@ -1971,7 +1968,7 @@
         <v>96</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F23" s="17">
         <v>5.0</v>
@@ -1980,31 +1977,31 @@
         <v>97</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
     </row>
     <row r="24">
-      <c r="A24" s="9"/>
+      <c r="A24" s="10"/>
       <c r="B24" s="15" t="s">
         <v>99</v>
       </c>
@@ -2015,7 +2012,7 @@
         <v>101</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F24" s="17">
         <v>3.0</v>
@@ -2024,31 +2021,31 @@
         <v>97</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I24" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="9"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="9"/>
-      <c r="Z24" s="9"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
     </row>
     <row r="25">
-      <c r="A25" s="9"/>
+      <c r="A25" s="10"/>
       <c r="B25" s="15" t="s">
         <v>103</v>
       </c>
@@ -2059,7 +2056,7 @@
         <v>105</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F25" s="17">
         <v>8.0</v>
@@ -2068,31 +2065,31 @@
         <v>97</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I25" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
-      <c r="Z25" s="9"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="10"/>
+      <c r="Z25" s="10"/>
     </row>
     <row r="26">
-      <c r="A26" s="9"/>
+      <c r="A26" s="10"/>
       <c r="B26" s="15" t="s">
         <v>107</v>
       </c>
@@ -2103,7 +2100,7 @@
         <v>109</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F26" s="17">
         <v>3.0</v>
@@ -2112,31 +2109,31 @@
         <v>97</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I26" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="10"/>
+      <c r="Z26" s="10"/>
     </row>
     <row r="27">
-      <c r="A27" s="9"/>
+      <c r="A27" s="10"/>
       <c r="B27" s="15" t="s">
         <v>111</v>
       </c>
@@ -2147,7 +2144,7 @@
         <v>113</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F27" s="17">
         <v>8.0</v>
@@ -2156,31 +2153,31 @@
         <v>97</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
+      <c r="V27" s="10"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="10"/>
+      <c r="Y27" s="10"/>
+      <c r="Z27" s="10"/>
     </row>
     <row r="28">
-      <c r="A28" s="9"/>
+      <c r="A28" s="10"/>
       <c r="B28" s="15" t="s">
         <v>114</v>
       </c>
@@ -2191,7 +2188,7 @@
         <v>116</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F28" s="17">
         <v>8.0</v>
@@ -2200,31 +2197,31 @@
         <v>97</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I28" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="10"/>
+      <c r="Z28" s="10"/>
     </row>
     <row r="29">
-      <c r="A29" s="9"/>
+      <c r="A29" s="10"/>
       <c r="B29" s="15" t="s">
         <v>118</v>
       </c>
@@ -2235,7 +2232,7 @@
         <v>120</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F29" s="17">
         <v>5.0</v>
@@ -2244,31 +2241,31 @@
         <v>97</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I29" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="9"/>
-      <c r="Z29" s="9"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
     </row>
     <row r="30">
-      <c r="A30" s="9"/>
+      <c r="A30" s="10"/>
       <c r="B30" s="15" t="s">
         <v>122</v>
       </c>
@@ -2279,7 +2276,7 @@
         <v>124</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F30" s="17">
         <v>5.0</v>
@@ -2288,31 +2285,31 @@
         <v>97</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
     </row>
     <row r="31">
-      <c r="A31" s="9"/>
+      <c r="A31" s="10"/>
       <c r="B31" s="15" t="s">
         <v>125</v>
       </c>
@@ -2323,7 +2320,7 @@
         <v>127</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="F31" s="17">
         <v>3.0</v>
@@ -2332,42 +2329,42 @@
         <v>97</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
+      <c r="Y31" s="10"/>
+      <c r="Z31" s="10"/>
     </row>
     <row r="32">
-      <c r="A32" s="9"/>
+      <c r="A32" s="10"/>
       <c r="B32" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>131</v>
-      </c>
       <c r="E32" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F32" s="17">
         <v>8.0</v>
@@ -2376,42 +2373,42 @@
         <v>97</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10"/>
+      <c r="V32" s="10"/>
+      <c r="W32" s="10"/>
+      <c r="X32" s="10"/>
+      <c r="Y32" s="10"/>
+      <c r="Z32" s="10"/>
     </row>
     <row r="33">
-      <c r="A33" s="9"/>
+      <c r="A33" s="10"/>
       <c r="B33" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="D33" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="E33" s="15" t="s">
         <v>134</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>135</v>
       </c>
       <c r="F33" s="17">
         <v>5.0</v>
@@ -2420,512 +2417,512 @@
         <v>97</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I33" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10"/>
+      <c r="B34" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9"/>
-      <c r="B34" s="15" t="s">
+      <c r="C34" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>139</v>
-      </c>
       <c r="E34" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="17">
         <v>8.0</v>
       </c>
       <c r="G34" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="H34" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" s="16" t="s">
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+      <c r="X34" s="10"/>
+      <c r="Y34" s="10"/>
+      <c r="Z34" s="10"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10"/>
+      <c r="B35" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9"/>
-      <c r="B35" s="15" t="s">
+      <c r="C35" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="D35" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>144</v>
-      </c>
       <c r="E35" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35" s="17">
         <v>13.0</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I35" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="10"/>
+      <c r="X35" s="10"/>
+      <c r="Y35" s="10"/>
+      <c r="Z35" s="10"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10"/>
+      <c r="B36" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9"/>
-      <c r="Y35" s="9"/>
-      <c r="Z35" s="9"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9"/>
-      <c r="B36" s="15" t="s">
+      <c r="C36" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="D36" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>148</v>
-      </c>
       <c r="E36" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" s="17">
         <v>8.0</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I36" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10"/>
+      <c r="V36" s="10"/>
+      <c r="W36" s="10"/>
+      <c r="X36" s="10"/>
+      <c r="Y36" s="10"/>
+      <c r="Z36" s="10"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10"/>
+      <c r="B37" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9"/>
-      <c r="B37" s="15" t="s">
+      <c r="C37" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="D37" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>152</v>
-      </c>
       <c r="E37" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F37" s="17">
         <v>5.0</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I37" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="10"/>
+      <c r="X37" s="10"/>
+      <c r="Y37" s="10"/>
+      <c r="Z37" s="10"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10"/>
+      <c r="B38" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
-      <c r="X37" s="9"/>
-      <c r="Y37" s="9"/>
-      <c r="Z37" s="9"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9"/>
-      <c r="B38" s="15" t="s">
+      <c r="C38" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="D38" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D38" s="16" t="s">
-        <v>156</v>
-      </c>
       <c r="E38" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F38" s="17">
         <v>5.0</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I38" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
+      <c r="U38" s="10"/>
+      <c r="V38" s="10"/>
+      <c r="W38" s="10"/>
+      <c r="X38" s="10"/>
+      <c r="Y38" s="10"/>
+      <c r="Z38" s="10"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10"/>
+      <c r="B39" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9"/>
-      <c r="Y38" s="9"/>
-      <c r="Z38" s="9"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9"/>
-      <c r="B39" s="15" t="s">
+      <c r="C39" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="D39" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="D39" s="16" t="s">
-        <v>160</v>
-      </c>
       <c r="E39" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F39" s="17">
         <v>8.0</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I39" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="10"/>
+      <c r="X39" s="10"/>
+      <c r="Y39" s="10"/>
+      <c r="Z39" s="10"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10"/>
+      <c r="B40" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9"/>
-      <c r="B40" s="15" t="s">
+      <c r="C40" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="D40" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="D40" s="16" t="s">
-        <v>164</v>
-      </c>
       <c r="E40" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40" s="17">
         <v>8.0</v>
       </c>
       <c r="G40" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="H40" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H40" s="18" t="s">
+      <c r="I40" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="I40" s="16" t="s">
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
+      <c r="U40" s="10"/>
+      <c r="V40" s="10"/>
+      <c r="W40" s="10"/>
+      <c r="X40" s="10"/>
+      <c r="Y40" s="10"/>
+      <c r="Z40" s="10"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10"/>
+      <c r="B41" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
-      <c r="U40" s="9"/>
-      <c r="V40" s="9"/>
-      <c r="W40" s="9"/>
-      <c r="X40" s="9"/>
-      <c r="Y40" s="9"/>
-      <c r="Z40" s="9"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9"/>
-      <c r="B41" s="15" t="s">
+      <c r="C41" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="D41" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D41" s="16" t="s">
-        <v>170</v>
-      </c>
       <c r="E41" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F41" s="17">
         <v>5.0</v>
       </c>
       <c r="G41" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="H41" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H41" s="18" t="s">
-        <v>166</v>
-      </c>
       <c r="I41" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
+      <c r="V41" s="10"/>
+      <c r="W41" s="10"/>
+      <c r="X41" s="10"/>
+      <c r="Y41" s="10"/>
+      <c r="Z41" s="10"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10"/>
+      <c r="B42" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
-      <c r="Y41" s="9"/>
-      <c r="Z41" s="9"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9"/>
-      <c r="B42" s="15" t="s">
+      <c r="C42" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="D42" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="D42" s="16" t="s">
-        <v>174</v>
-      </c>
       <c r="E42" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F42" s="17">
         <v>8.0</v>
       </c>
       <c r="G42" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="H42" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H42" s="18" t="s">
-        <v>166</v>
-      </c>
       <c r="I42" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
+      <c r="T42" s="10"/>
+      <c r="U42" s="10"/>
+      <c r="V42" s="10"/>
+      <c r="W42" s="10"/>
+      <c r="X42" s="10"/>
+      <c r="Y42" s="10"/>
+      <c r="Z42" s="10"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10"/>
+      <c r="B43" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
-      <c r="R42" s="9"/>
-      <c r="S42" s="9"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9"/>
-      <c r="B43" s="15" t="s">
+      <c r="C43" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="D43" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="D43" s="16" t="s">
-        <v>178</v>
-      </c>
       <c r="E43" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F43" s="17">
         <v>8.0</v>
       </c>
       <c r="G43" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="H43" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H43" s="18" t="s">
-        <v>166</v>
-      </c>
       <c r="I43" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="10"/>
+      <c r="V43" s="10"/>
+      <c r="W43" s="10"/>
+      <c r="X43" s="10"/>
+      <c r="Y43" s="10"/>
+      <c r="Z43" s="10"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10"/>
+      <c r="B44" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="9"/>
-      <c r="B44" s="15" t="s">
+      <c r="C44" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="D44" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="D44" s="16" t="s">
-        <v>182</v>
-      </c>
       <c r="E44" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F44" s="17">
         <v>5.0</v>
       </c>
       <c r="G44" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="H44" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H44" s="18" t="s">
-        <v>166</v>
-      </c>
       <c r="I44" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9"/>
-      <c r="R44" s="9"/>
-      <c r="S44" s="9"/>
-      <c r="T44" s="9"/>
-      <c r="U44" s="9"/>
-      <c r="V44" s="9"/>
-      <c r="W44" s="9"/>
-      <c r="X44" s="9"/>
-      <c r="Y44" s="9"/>
-      <c r="Z44" s="9"/>
+        <v>182</v>
+      </c>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10"/>
+      <c r="U44" s="10"/>
+      <c r="V44" s="10"/>
+      <c r="W44" s="10"/>
+      <c r="X44" s="10"/>
+      <c r="Y44" s="10"/>
+      <c r="Z44" s="10"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1"/>
@@ -9334,7 +9331,7 @@
     <row r="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -9363,8 +9360,8 @@
     </row>
     <row r="2">
       <c r="A2" s="1"/>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -9421,11 +9418,11 @@
     </row>
     <row r="4">
       <c r="A4" s="1"/>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>5</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>12</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -9453,11 +9450,11 @@
     </row>
     <row r="5">
       <c r="A5" s="1"/>
-      <c r="B5" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>16</v>
+      <c r="B5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -9485,11 +9482,11 @@
     </row>
     <row r="6">
       <c r="A6" s="1"/>
-      <c r="B6" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>18</v>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -9517,11 +9514,11 @@
     </row>
     <row r="7">
       <c r="A7" s="1"/>
-      <c r="B7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>20</v>
+      <c r="B7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -9549,11 +9546,11 @@
     </row>
     <row r="8">
       <c r="A8" s="1"/>
-      <c r="B8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>22</v>
+      <c r="B8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -9581,11 +9578,11 @@
     </row>
     <row r="9" ht="50.25" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>24</v>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -9613,11 +9610,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1"/>
-      <c r="B10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>25</v>
+      <c r="B10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -9645,11 +9642,11 @@
     </row>
     <row r="11">
       <c r="A11" s="1"/>
-      <c r="B11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>26</v>
+      <c r="B11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -9677,11 +9674,11 @@
     </row>
     <row r="12">
       <c r="A12" s="1"/>
-      <c r="B12" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>31</v>
+      <c r="B12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
